--- a/AtchisonRegime/Outputs/USA/USA_Earnings_Yield/df_regSummary_USA_Earnings_Yield.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Earnings_Yield/df_regSummary_USA_Earnings_Yield.xlsx
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>1.542439071048227</v>
+        <v>1.308689114876782</v>
       </c>
       <c r="H2" t="n">
-        <v>3.24235854617211</v>
+        <v>3.55134634593727</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.54358074682365</v>
+        <v>-8.508809044323931</v>
       </c>
       <c r="J2" t="n">
         <v>6.95169290448147</v>
       </c>
       <c r="K2" t="n">
-        <v>32.55813953488372</v>
+        <v>33.07692307692307</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1423933908336546</v>
+        <v>0.1184859468952383</v>
       </c>
       <c r="O2" t="n">
         <v>-0.02750881203672606</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4048642891078003</v>
+        <v>0.2853270694157186</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>7.285268265153571</v>
       </c>
       <c r="K3" t="n">
-        <v>20.15503875968992</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7.521483003263831</v>
       </c>
       <c r="K4" t="n">
-        <v>22.48062015503876</v>
+        <v>22.30769230769231</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>8.975974874825891</v>
       </c>
       <c r="K5" t="n">
-        <v>24.8062015503876</v>
+        <v>24.61538461538462</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
